--- a/Team-Data/2007-08/4-3-2007-08.xlsx
+++ b/Team-Data/2007-08/4-3-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -781,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
         <v>19</v>
@@ -951,7 +1018,7 @@
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1121,7 +1188,7 @@
         <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
         <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.392</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1225,10 +1292,10 @@
         <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
@@ -1246,25 +1313,25 @@
         <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R5" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S5" t="n">
         <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.3</v>
+        <v>43.5</v>
       </c>
       <c r="U5" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V5" t="n">
         <v>14.5</v>
       </c>
       <c r="W5" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X5" t="n">
         <v>5.2</v>
@@ -1279,13 +1346,13 @@
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1324,10 +1391,10 @@
         <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS5" t="n">
         <v>18</v>
@@ -1339,13 +1406,13 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
         <v>29</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1456,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="n">
         <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
-        <v>0.553</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
         <v>81.8</v>
@@ -1413,10 +1480,10 @@
         <v>0.441</v>
       </c>
       <c r="L6" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N6" t="n">
         <v>0.361</v>
@@ -1461,13 +1528,13 @@
         <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
@@ -1509,13 +1576,13 @@
         <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
         <v>24</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1661,10 +1728,10 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>12</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
@@ -2317,7 +2384,7 @@
         <v>36.7</v>
       </c>
       <c r="J11" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K11" t="n">
         <v>0.449</v>
@@ -2329,7 +2396,7 @@
         <v>20.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O11" t="n">
         <v>16.4</v>
@@ -2338,7 +2405,7 @@
         <v>22.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R11" t="n">
         <v>12.3</v>
@@ -2347,7 +2414,7 @@
         <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U11" t="n">
         <v>21.4</v>
@@ -2368,34 +2435,34 @@
         <v>19.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB11" t="n">
         <v>96.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK11" t="n">
         <v>18</v>
@@ -2416,10 +2483,10 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
         <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>0.303</v>
+        <v>0.307</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K13" t="n">
         <v>0.439</v>
@@ -2693,25 +2760,25 @@
         <v>13.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.325</v>
+        <v>0.324</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P13" t="n">
         <v>26.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.786</v>
+        <v>0.788</v>
       </c>
       <c r="R13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S13" t="n">
         <v>30.3</v>
       </c>
       <c r="T13" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
@@ -2729,7 +2796,7 @@
         <v>4.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
@@ -2738,10 +2805,10 @@
         <v>94.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,10 +2820,10 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ13" t="n">
         <v>28</v>
@@ -2774,16 +2841,16 @@
         <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP13" t="n">
         <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
         <v>16</v>
@@ -2792,13 +2859,13 @@
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>15</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,13 +3184,13 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI15" t="n">
         <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,10 +3366,10 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3490,7 +3557,7 @@
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -3523,7 +3590,7 @@
         <v>16</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>22</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-7</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
         <v>29</v>
@@ -4242,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>9</v>
@@ -4418,7 +4485,7 @@
         <v>3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>14</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
@@ -4633,7 +4700,7 @@
         <v>16</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>4.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>6</v>
@@ -4806,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ24" t="n">
         <v>9</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
         <v>38</v>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.507</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4874,28 +4941,28 @@
         <v>6.6</v>
       </c>
       <c r="M25" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O25" t="n">
         <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R25" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S25" t="n">
         <v>29.7</v>
       </c>
       <c r="T25" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="U25" t="n">
         <v>21.1</v>
@@ -4910,34 +4977,34 @@
         <v>4.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>27</v>
@@ -4946,7 +5013,7 @@
         <v>22</v>
       </c>
       <c r="AK25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,7 +5022,7 @@
         <v>16</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>24</v>
@@ -4964,19 +5031,19 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
@@ -4988,7 +5055,7 @@
         <v>21</v>
       </c>
       <c r="AY25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F26" t="n">
         <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>0.467</v>
+        <v>0.459</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5056,16 +5123,16 @@
         <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="P26" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="Q26" t="n">
         <v>0.797</v>
@@ -5074,10 +5141,10 @@
         <v>10.2</v>
       </c>
       <c r="S26" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T26" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U26" t="n">
         <v>19.1</v>
@@ -5086,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="W26" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X26" t="n">
         <v>4.2</v>
@@ -5098,25 +5165,25 @@
         <v>22.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>7</v>
@@ -5125,7 +5192,7 @@
         <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
         <v>10</v>
@@ -5137,7 +5204,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5149,7 +5216,7 @@
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
         <v>19</v>
@@ -5164,7 +5231,7 @@
         <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -5301,7 +5368,7 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
         <v>24</v>
@@ -5331,7 +5398,7 @@
         <v>15</v>
       </c>
       <c r="AR27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
         <v>9</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5519,7 +5586,7 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,7 +5732,7 @@
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6056,7 +6123,7 @@
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR31" t="n">
         <v>9</v>
@@ -6074,7 +6141,7 @@
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-3-2007-08</t>
+          <t>2008-04-03</t>
         </is>
       </c>
     </row>
